--- a/outputs/per-fund/vc-investments-delphi-ventures.xlsx
+++ b/outputs/per-fund/vc-investments-delphi-ventures.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Only Delphi Ventures. The full overview with all twenty funds is in vc-investments-full.xlsx.</t>
+          <t>Only Delphi Ventures. The full overview with all 59 funds is in vc-investments-full.xlsx.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>The twenty funds, with control totals per external source.</t>
+          <t>The 59 funds, with control totals per external source.</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>One row per company in which at least one of the twenty funds invested.</t>
+          <t>One row per company in which at least one of these 59 funds invested.</t>
         </is>
       </c>
     </row>
@@ -22256,11 +22256,11 @@
         <v>1</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, framework-ventures</t>
+          <t>delphi-ventures, framework-ventures, iosg-ventures</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
@@ -22319,11 +22319,11 @@
         <v>1</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, electric-capital, robot-ventures</t>
+          <t>alliance-dao, coinfund, delphi-ventures, electric-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
@@ -22382,11 +22382,11 @@
         <v>0</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>alliance-dao, delphi-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
@@ -22445,11 +22445,11 @@
         <v>1</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, delphi-ventures</t>
+          <t>coinbase-ventures, delphi-ventures, hashed, hypersphere, yzi-labs</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -22508,11 +22508,11 @@
         <v>0</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>alliance-dao, delphi-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -22571,11 +22571,11 @@
         <v>1</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>alameda-research, delphi-ventures, mechanism-capital</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -22756,11 +22756,11 @@
         <v>0</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>animoca-brands, delphi-ventures, polygon-ventures, sevenx-ventures, sfermion</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -22815,11 +22815,11 @@
         <v>1</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, delphi-ventures, dragonfly, paradigm, robot-ventures</t>
+          <t>alameda-research, coinbase-ventures, delphi-ventures, digital-currency-group, dragonfly, paradigm, robot-ventures</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -22878,11 +22878,11 @@
         <v>3</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, framework-ventures</t>
+          <t>blockchain-capital, cms-holdings, coinfund, delphi-ventures, framework-ventures, mechanism-capital</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
@@ -22941,11 +22941,11 @@
         <v>1</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, fenbushi-capital, longhash-ventures, okx-ventures, parafi-capital, spartan-group</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -23000,11 +23000,11 @@
         <v>2</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital, robot-ventures</t>
+          <t>alameda-research, alliance-dao, delphi-ventures, fenbushi-capital, iosg-ventures, multicoin-capital, okx-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
@@ -23063,11 +23063,11 @@
         <v>0</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>animoca-brands, animoca-brands-japan, delphi-ventures, mechanism-capital</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
@@ -23126,11 +23126,11 @@
         <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>alameda-research, delphi-ventures, mechanism-capital</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
@@ -23189,11 +23189,11 @@
         <v>1</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, delphi-ventures, electric-capital, paradigm, polychain</t>
+          <t>a16z-crypto, cms-holdings, cmt-digital, delphi-ventures, electric-capital, hashkey-capital, paradigm, polychain</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -23252,11 +23252,11 @@
         <v>0</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>animoca-brands, delphi-ventures, mechanism-capital, parafi-capital, sevenx-ventures, sfermion</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
@@ -23315,11 +23315,11 @@
         <v>0</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, hashed</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -23378,11 +23378,11 @@
         <v>0</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>alameda-research, alliance-dao, cms-holdings, delphi-ventures, parafi-capital</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -23441,11 +23441,11 @@
         <v>0</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, lemniscap</t>
+          <t>delphi-ventures, lemniscap, mechanism-capital</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
@@ -23502,11 +23502,11 @@
         <v>0</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital</t>
+          <t>delphi-ventures, multicoin-capital, parafi-capital, spartan-group</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -23565,11 +23565,11 @@
         <v>0</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital, semantic-ventures</t>
+          <t>alliance-dao, delphi-ventures, multicoin-capital, semantic-ventures</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
@@ -23693,11 +23693,11 @@
         <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, delphi-ventures, framework-ventures</t>
+          <t>alliance-dao, coinbase-ventures, delphi-ventures, framework-ventures, hypersphere, parafi-capital</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -23756,11 +23756,11 @@
         <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, paradigm, robot-ventures</t>
+          <t>delphi-ventures, mechanism-capital, paradigm, robot-ventures</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -23815,11 +23815,11 @@
         <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, lemniscap</t>
+          <t>delphi-ventures, gsr, lemniscap, solana-ventures</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -23874,11 +23874,11 @@
         <v>0</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, mechanism-capital</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -23937,11 +23937,11 @@
         <v>2</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital, robot-ventures</t>
+          <t>delphi-ventures, hypersphere, multicoin-capital, robot-ventures, spartan-group, yzi-labs</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
@@ -24063,11 +24063,11 @@
         <v>1</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, delphi-ventures, figment-capital</t>
+          <t>alliance-dao, coinbase-ventures, delphi-ventures, figment-capital, iosg-ventures</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -24126,11 +24126,11 @@
         <v>3</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, dragonfly</t>
+          <t>alameda-research, arrington-capital, cmt-digital, delphi-ventures, dragonfly, fenbushi-capital, hashed, sfermion</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -24191,11 +24191,11 @@
         <v>1</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, mechanism-capital</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
@@ -24250,11 +24250,11 @@
         <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital</t>
+          <t>delphi-ventures, gsr, multicoin-capital, parafi-capital, sequoia-capital, spartan-group</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
@@ -24313,11 +24313,11 @@
         <v>0</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>alliance-dao, delphi-ventures, digital-currency-group, hashed</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -24372,11 +24372,11 @@
         <v>0</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, gsr, huobi-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -24435,11 +24435,11 @@
         <v>0</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, framework-ventures</t>
+          <t>alameda-research, cms-holdings, delphi-ventures, framework-ventures</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
@@ -24624,11 +24624,11 @@
         <v>0</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>arrington-capital, delphi-ventures, parafi-capital</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
@@ -24746,11 +24746,11 @@
         <v>0</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>alliance-dao, cms-holdings, delphi-ventures, mechanism-capital, spartan-group</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -24809,11 +24809,11 @@
         <v>0</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>1kx, delphi-ventures</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -24872,11 +24872,11 @@
         <v>1</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>arrington-capital, borderless-capital, delphi-ventures, mechanism-capital</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -24935,11 +24935,11 @@
         <v>0</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>animoca-brands, delphi-ventures</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -24998,11 +24998,11 @@
         <v>0</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>alameda-research, cms-holdings, delphi-ventures, gsr, solana-ventures</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -25057,11 +25057,11 @@
         <v>0</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>alliance-dao, cms-holdings, delphi-ventures, digital-currency-group, mechanism-capital, parafi-capital, spartan-group</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -25120,11 +25120,11 @@
         <v>3</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, gnosis-vc</t>
+          <t>alliance-dao, arrington-capital, delphi-ventures, gnosis-vc</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -25246,11 +25246,11 @@
         <v>0</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>alameda-research, animoca-brands, delphi-ventures, hashkey-capital, mechanism-capital, yzi-labs</t>
         </is>
       </c>
       <c r="M50" s="10" t="n"/>
@@ -25305,11 +25305,11 @@
         <v>2</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, delphi-ventures</t>
+          <t>a16z-crypto, delphi-ventures, hashed, mechanism-capital, sfermion</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
@@ -25368,11 +25368,11 @@
         <v>0</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, dragonfly</t>
+          <t>alliance-dao, animoca-brands, cmt-digital, delphi-ventures, dragonfly, sfermion</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
@@ -25494,11 +25494,11 @@
         <v>0</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, delphi-ventures</t>
+          <t>alameda-research, alliance-dao, coinbase-ventures, delphi-ventures, hashed</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -25616,11 +25616,11 @@
         <v>0</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>animoca-brands, delphi-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -25679,11 +25679,11 @@
         <v>0</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>animoca-brands, delphi-ventures, huobi-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
@@ -25801,11 +25801,11 @@
         <v>1</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, framework-ventures, polychain</t>
+          <t>blockchain-capital, coinfund, delphi-ventures, framework-ventures, mechanism-capital, polychain</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
@@ -25864,11 +25864,11 @@
         <v>0</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, framework-ventures, polychain</t>
+          <t>blockchain-capital, coinfund, delphi-ventures, framework-ventures, mechanism-capital, polychain</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -25925,11 +25925,11 @@
         <v>0</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, robot-ventures</t>
+          <t>1kx, blockchain-capital, delphi-ventures, hack-vc, longhash-ventures, robot-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
@@ -26053,11 +26053,11 @@
         <v>0</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>alameda-research, amber-group, delphi-ventures</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
@@ -26116,11 +26116,11 @@
         <v>0</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, framework-ventures</t>
+          <t>delphi-ventures, framework-ventures, iosg-ventures</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
@@ -26177,11 +26177,11 @@
         <v>2</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, hashed</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
@@ -26297,11 +26297,11 @@
         <v>0</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>arrington-capital, delphi-ventures, hashed, jump-crypto</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
@@ -26547,11 +26547,11 @@
         <v>0</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>amber-group, animoca-brands, delphi-ventures, iosg-ventures, sevenx-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
@@ -26673,11 +26673,11 @@
         <v>0</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>animoca-brands, delphi-ventures, mechanism-capital, mh-ventures, yzi-labs</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
@@ -26736,11 +26736,11 @@
         <v>0</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, parafi-capital</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
@@ -26799,11 +26799,11 @@
         <v>3</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, delphi-ventures, lemniscap</t>
+          <t>coinbase-ventures, delphi-ventures, lemniscap, sfermion</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
@@ -26862,11 +26862,11 @@
         <v>0</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, gnosis-vc</t>
+          <t>alliance-dao, arrington-capital, delphi-ventures, gnosis-vc, hypersphere, sevenx-ventures</t>
         </is>
       </c>
       <c r="M76" s="7" t="inlineStr">
@@ -26925,11 +26925,11 @@
         <v>0</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>alameda-research, animoca-brands, cms-holdings, delphi-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
@@ -26988,11 +26988,11 @@
         <v>0</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, dragonfly</t>
+          <t>delphi-ventures, dragonfly, mechanism-capital</t>
         </is>
       </c>
       <c r="M78" s="7" t="inlineStr">
@@ -27051,11 +27051,11 @@
         <v>0</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, framework-ventures, multicoin-capital, robot-ventures</t>
+          <t>alameda-research, delphi-ventures, framework-ventures, multicoin-capital, robot-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
@@ -27114,11 +27114,11 @@
         <v>0</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, lemniscap</t>
+          <t>1kx, big-brain-holdings, delphi-ventures, lemniscap, mirana-ventures</t>
         </is>
       </c>
       <c r="M80" s="7" t="inlineStr">
@@ -27179,11 +27179,11 @@
         <v>1</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, delphi-ventures, multicoin-capital</t>
+          <t>coinbase-ventures, delphi-ventures, gsr, hypersphere, multicoin-capital</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
@@ -27242,11 +27242,11 @@
         <v>0</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, dragonfly</t>
+          <t>delphi-ventures, dragonfly, parafi-capital</t>
         </is>
       </c>
       <c r="M82" s="7" t="inlineStr">
@@ -27305,11 +27305,11 @@
         <v>1</v>
       </c>
       <c r="K83" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital</t>
+          <t>alliance-dao, cms-holdings, delphi-ventures, digital-currency-group, mechanism-capital, multicoin-capital, parafi-capital, spartan-group</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
@@ -27364,11 +27364,11 @@
         <v>0</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, hashed, spartan-group</t>
         </is>
       </c>
       <c r="M84" s="7" t="inlineStr">
@@ -27429,11 +27429,11 @@
         <v>2</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, coinbase-ventures, delphi-ventures, figment-capital, maven11, polychain</t>
+          <t>bain-capital-crypto, blockchain-capital, coinbase-ventures, delphi-ventures, figment-capital, galaxy-digital, jump-crypto, maven11, mh-ventures, polychain, spartan-group</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
@@ -27492,11 +27492,11 @@
         <v>2</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, polygon-ventures</t>
         </is>
       </c>
       <c r="M86" s="7" t="inlineStr">
@@ -27551,11 +27551,11 @@
         <v>4</v>
       </c>
       <c r="K87" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, delphi-ventures</t>
+          <t>coinbase-ventures, delphi-ventures, hashed, mechanism-capital</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
@@ -27677,11 +27677,11 @@
         <v>1</v>
       </c>
       <c r="K89" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, figment-capital, lemniscap, maven11, robot-ventures</t>
+          <t>1kx, delphi-ventures, figment-capital, lemniscap, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
@@ -27738,11 +27738,11 @@
         <v>1</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, hashkey-capital</t>
         </is>
       </c>
       <c r="M90" s="7" t="inlineStr">
@@ -27801,11 +27801,11 @@
         <v>1</v>
       </c>
       <c r="K91" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital</t>
+          <t>delphi-ventures, multicoin-capital, polygon-ventures</t>
         </is>
       </c>
       <c r="M91" s="10" t="n"/>
@@ -27856,11 +27856,11 @@
         <v>1</v>
       </c>
       <c r="K92" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, electric-capital</t>
+          <t>delphi-ventures, electric-capital, mh-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M92" s="7" t="inlineStr">
@@ -27919,11 +27919,11 @@
         <v>2</v>
       </c>
       <c r="K93" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, mirana-ventures</t>
         </is>
       </c>
       <c r="M93" s="7" t="inlineStr">
@@ -27980,11 +27980,11 @@
         <v>2</v>
       </c>
       <c r="K94" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, semantic-ventures</t>
+          <t>coinfund, delphi-ventures, longhash-ventures, semantic-ventures, yzi-labs</t>
         </is>
       </c>
       <c r="M94" s="7" t="inlineStr">
@@ -28041,11 +28041,11 @@
         <v>1</v>
       </c>
       <c r="K95" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>big-brain-holdings, delphi-ventures, okx-ventures</t>
         </is>
       </c>
       <c r="M95" s="7" t="inlineStr">
@@ -28104,11 +28104,11 @@
         <v>1</v>
       </c>
       <c r="K96" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, dragonfly</t>
+          <t>cmt-digital, delphi-ventures, dragonfly, gsr, mirana-ventures, okx-ventures</t>
         </is>
       </c>
       <c r="M96" s="7" t="inlineStr">
@@ -28167,11 +28167,11 @@
         <v>1</v>
       </c>
       <c r="K97" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, delphi-ventures, figment-capital, maven11</t>
+          <t>bain-capital-crypto, blockchain-capital, delphi-ventures, fenbushi-capital, figment-capital, galaxy-digital, iosg-ventures, maven11</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
@@ -28293,11 +28293,11 @@
         <v>2</v>
       </c>
       <c r="K99" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>cms-holdings, delphi-ventures, hack-vc</t>
         </is>
       </c>
       <c r="M99" s="7" t="inlineStr">
@@ -28356,11 +28356,11 @@
         <v>1</v>
       </c>
       <c r="K100" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital</t>
+          <t>delphi-ventures, jump-crypto, multicoin-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M100" s="7" t="inlineStr">
@@ -28535,11 +28535,11 @@
         <v>0</v>
       </c>
       <c r="K103" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital</t>
+          <t>borderless-capital, cmt-digital, delphi-ventures, multicoin-capital</t>
         </is>
       </c>
       <c r="M103" s="7" t="inlineStr">
@@ -28655,11 +28655,11 @@
         <v>2</v>
       </c>
       <c r="K105" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>cms-holdings, delphi-ventures, foresight-ventures, okx-ventures</t>
         </is>
       </c>
       <c r="M105" s="7" t="inlineStr">
@@ -28775,11 +28775,11 @@
         <v>0</v>
       </c>
       <c r="K107" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>amber-group, animoca-brands, delphi-ventures, foresight-ventures</t>
         </is>
       </c>
       <c r="M107" s="7" t="inlineStr">
@@ -28895,11 +28895,11 @@
         <v>0</v>
       </c>
       <c r="K109" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>amber-group, delphi-ventures, foresight-ventures, mechanism-capital, sfermion, spartan-group</t>
         </is>
       </c>
       <c r="M109" s="7" t="inlineStr">
@@ -28958,11 +28958,11 @@
         <v>1</v>
       </c>
       <c r="K110" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, galaxy-digital</t>
         </is>
       </c>
       <c r="M110" s="7" t="inlineStr">
@@ -29021,11 +29021,11 @@
         <v>2</v>
       </c>
       <c r="K111" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, figment-capital</t>
+          <t>big-brain-holdings, delphi-ventures, figment-capital, hack-vc</t>
         </is>
       </c>
       <c r="M111" s="7" t="inlineStr">
@@ -29084,11 +29084,11 @@
         <v>2</v>
       </c>
       <c r="K112" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, maven11, polychain</t>
+          <t>delphi-ventures, fenbushi-capital, hack-vc, maven11, polychain</t>
         </is>
       </c>
       <c r="M112" s="7" t="inlineStr">
@@ -29143,11 +29143,11 @@
         <v>1</v>
       </c>
       <c r="K113" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, dragonfly, maven11</t>
+          <t>delphi-ventures, dragonfly, maven11, okx-ventures</t>
         </is>
       </c>
       <c r="M113" s="7" t="inlineStr">
@@ -29204,11 +29204,11 @@
         <v>1</v>
       </c>
       <c r="K114" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, mechanism-capital, sfermion</t>
         </is>
       </c>
       <c r="M114" s="7" t="inlineStr">
@@ -29263,11 +29263,11 @@
         <v>0</v>
       </c>
       <c r="K115" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M115" s="7" t="inlineStr">
@@ -29326,11 +29326,11 @@
         <v>1</v>
       </c>
       <c r="K116" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital</t>
+          <t>animoca-brands, delphi-ventures, foresight-ventures, hack-vc, longhash-ventures, mh-ventures, multicoin-capital, okx-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M116" s="7" t="inlineStr">
@@ -29448,11 +29448,11 @@
         <v>1</v>
       </c>
       <c r="K118" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>alliance-dao, animoca-brands, delphi-ventures, hack-vc, longhash-ventures, okx-ventures, polygon-ventures</t>
         </is>
       </c>
       <c r="M118" s="7" t="inlineStr">
@@ -29570,11 +29570,11 @@
         <v>2</v>
       </c>
       <c r="K120" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, delphi-ventures</t>
+          <t>coinbase-ventures, delphi-ventures, foresight-ventures, hashed, mechanism-capital, mh-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M120" s="7" t="inlineStr">
@@ -29633,11 +29633,11 @@
         <v>3</v>
       </c>
       <c r="K121" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>big-brain-holdings, delphi-ventures, mechanism-capital</t>
         </is>
       </c>
       <c r="M121" s="7" t="inlineStr">
@@ -29690,11 +29690,11 @@
         <v>0</v>
       </c>
       <c r="K122" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, longhash-ventures, okx-ventures</t>
         </is>
       </c>
       <c r="M122" s="7" t="inlineStr">
@@ -29747,11 +29747,11 @@
         <v>0</v>
       </c>
       <c r="K123" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>coinfund, delphi-ventures</t>
         </is>
       </c>
       <c r="M123" s="7" t="inlineStr">
@@ -29806,11 +29806,11 @@
         <v>1</v>
       </c>
       <c r="K124" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>animoca-brands, delphi-ventures, mechanism-capital, mh-ventures, polygon-ventures</t>
         </is>
       </c>
       <c r="M124" s="7" t="inlineStr">
@@ -29865,11 +29865,11 @@
         <v>0</v>
       </c>
       <c r="K125" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>big-brain-holdings, delphi-ventures, foresight-ventures</t>
         </is>
       </c>
       <c r="M125" s="7" t="inlineStr">
@@ -29928,11 +29928,11 @@
         <v>0</v>
       </c>
       <c r="K126" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>cms-holdings, delphi-ventures</t>
         </is>
       </c>
       <c r="M126" s="7" t="inlineStr">
@@ -29991,11 +29991,11 @@
         <v>3</v>
       </c>
       <c r="K127" s="6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, founders-fund, framework-ventures, pantera, robot-ventures</t>
+          <t>arrington-capital, delphi-ventures, foresight-ventures, founders-fund, framework-ventures, hack-vc, hashkey-capital, hypersphere, mh-ventures, mirana-ventures, pantera, robot-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M127" s="7" t="inlineStr">
@@ -30050,11 +30050,11 @@
         <v>5</v>
       </c>
       <c r="K128" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, gsr</t>
         </is>
       </c>
       <c r="M128" s="7" t="inlineStr">
@@ -30113,11 +30113,11 @@
         <v>3</v>
       </c>
       <c r="K129" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>animoca-brands, delphi-ventures</t>
         </is>
       </c>
       <c r="M129" s="7" t="inlineStr">
@@ -30176,11 +30176,11 @@
         <v>1</v>
       </c>
       <c r="K130" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, delphi-ventures</t>
+          <t>alliance-dao, cyber-fund, delphi-ventures, longhash-ventures</t>
         </is>
       </c>
       <c r="M130" s="7" t="inlineStr">
@@ -30241,11 +30241,11 @@
         <v>1</v>
       </c>
       <c r="K131" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, figment-capital, robot-ventures, semantic-ventures</t>
+          <t>delphi-ventures, figment-capital, robot-ventures, semantic-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M131" s="7" t="inlineStr">
@@ -30426,11 +30426,11 @@
         <v>1</v>
       </c>
       <c r="K134" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, hack-vc</t>
         </is>
       </c>
       <c r="M134" s="7" t="inlineStr">
@@ -30483,11 +30483,11 @@
         <v>0</v>
       </c>
       <c r="K135" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, hashkey-capital</t>
         </is>
       </c>
       <c r="M135" s="10" t="n"/>
@@ -30727,11 +30727,11 @@
         <v>0</v>
       </c>
       <c r="K139" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>animoca-brands, delphi-ventures, foresight-ventures, hack-vc, okx-ventures</t>
         </is>
       </c>
       <c r="M139" s="7" t="inlineStr">
@@ -30786,11 +30786,11 @@
         <v>1</v>
       </c>
       <c r="K140" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, figment-capital, robot-ventures</t>
+          <t>alliance-dao, big-brain-holdings, delphi-ventures, figment-capital, mechanism-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M140" s="7" t="inlineStr">
@@ -30908,11 +30908,11 @@
         <v>0</v>
       </c>
       <c r="K142" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>animoca-brands, delphi-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M142" s="7" t="inlineStr">
@@ -30967,11 +30967,11 @@
         <v>1</v>
       </c>
       <c r="K143" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>animoca-brands, delphi-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M143" s="7" t="inlineStr">
@@ -31026,11 +31026,11 @@
         <v>0</v>
       </c>
       <c r="K144" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, hack-vc</t>
         </is>
       </c>
       <c r="M144" s="7" t="inlineStr">
@@ -31089,11 +31089,11 @@
         <v>1</v>
       </c>
       <c r="K145" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, delphi-ventures, framework-ventures</t>
+          <t>1kx, coinbase-ventures, delphi-ventures, framework-ventures</t>
         </is>
       </c>
       <c r="M145" s="7" t="inlineStr">
@@ -31152,11 +31152,11 @@
         <v>0</v>
       </c>
       <c r="K146" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>amber-group, delphi-ventures</t>
         </is>
       </c>
       <c r="M146" s="7" t="inlineStr">
@@ -31213,11 +31213,11 @@
         <v>2</v>
       </c>
       <c r="K147" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, dragonfly, multicoin-capital</t>
+          <t>borderless-capital, delphi-ventures, dragonfly, gsr, mh-ventures, multicoin-capital</t>
         </is>
       </c>
       <c r="M147" s="7" t="inlineStr">
@@ -31335,11 +31335,11 @@
         <v>1</v>
       </c>
       <c r="K149" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>big-brain-holdings, borderless-capital, delphi-ventures, gsr</t>
         </is>
       </c>
       <c r="M149" s="7" t="inlineStr">
@@ -31398,11 +31398,11 @@
         <v>1</v>
       </c>
       <c r="K150" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, maven11, robot-ventures</t>
+          <t>delphi-ventures, maven11, mechanism-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M150" s="7" t="inlineStr">
@@ -31461,11 +31461,11 @@
         <v>2</v>
       </c>
       <c r="K151" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>amber-group, arrington-capital, cms-holdings, delphi-ventures, hack-vc</t>
         </is>
       </c>
       <c r="M151" s="7" t="inlineStr">
@@ -31520,11 +31520,11 @@
         <v>0</v>
       </c>
       <c r="K152" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>big-brain-holdings, delphi-ventures, mechanism-capital</t>
         </is>
       </c>
       <c r="M152" s="7" t="inlineStr">
@@ -31642,11 +31642,11 @@
         <v>2</v>
       </c>
       <c r="K154" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, hashed</t>
         </is>
       </c>
       <c r="M154" s="7" t="inlineStr">
@@ -31705,11 +31705,11 @@
         <v>1</v>
       </c>
       <c r="K155" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, delphi-ventures</t>
+          <t>animoca-brands, cyber-fund, delphi-ventures, hashkey-capital</t>
         </is>
       </c>
       <c r="M155" s="7" t="inlineStr">
@@ -31764,11 +31764,11 @@
         <v>0</v>
       </c>
       <c r="K156" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, hashkey-capital</t>
         </is>
       </c>
       <c r="M156" s="7" t="inlineStr">
@@ -31823,11 +31823,11 @@
         <v>3</v>
       </c>
       <c r="K157" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures</t>
+          <t>delphi-ventures, hack-vc</t>
         </is>
       </c>
       <c r="M157" s="7" t="inlineStr">
@@ -31886,11 +31886,11 @@
         <v>0</v>
       </c>
       <c r="K158" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, delphi-ventures</t>
+          <t>cyber-fund, delphi-ventures, gsr</t>
         </is>
       </c>
       <c r="M158" s="7" t="inlineStr">
@@ -39809,19 +39809,19 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Fondspagina toont een vast maximum aantal regels; dit is een displaylimiet en geen portefeuilletotaal.</t>
+          <t>The fund page shows a fixed maximum number of rows; this is a display limit, not a portfolio total.</t>
         </is>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>Pagina levert geen leesbare portefeuillelijst in statische HTML (client-side gerenderd). Niet geteld; geen schatting gemaakt.</t>
+          <t>Page delivers no readable portfolio list in static HTML (client-side rendered). Not counted; no estimate made.</t>
         </is>
       </c>
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>Geen telling verkregen; niet geschat.</t>
+          <t>No count obtained; not estimated.</t>
         </is>
       </c>
       <c r="K2" s="6" t="n">
@@ -39829,7 +39829,7 @@
       </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>`investments` is CryptoRanks eigen telling. De zichtbare portefeuillelijst toont zonder account maar tien regels; die lijst is niet gebruikt.</t>
+          <t>`investments` is CryptoRank's own count. The visible portfolio list shows only ten rows without an account; that list was not used.</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
